--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2019_atacama.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2019_atacama.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>30.6190587013731</v>
+      </c>
+      <c r="C2">
         <v>21.45043770923217</v>
-      </c>
-      <c r="C2">
-        <v>30.6190587013731</v>
       </c>
       <c r="D2">
         <v>4.661909530963111</v>
       </c>
       <c r="E2">
-        <v>14.10568076803089</v>
+        <v>20.13491161876284</v>
       </c>
       <c r="F2">
         <v>65.75940761320628</v>
       </c>
       <c r="G2">
-        <v>20.13491161876284</v>
+        <v>14.10568076803089</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>32.94453701499643</v>
+      </c>
+      <c r="C3">
         <v>26.17630722843767</v>
-      </c>
-      <c r="C3">
-        <v>32.94453701499643</v>
       </c>
       <c r="D3">
         <v>3.820248560169748</v>
       </c>
       <c r="E3">
-        <v>16.45058342475317</v>
+        <v>20.70409893288122</v>
       </c>
       <c r="F3">
         <v>62.84531764236561</v>
       </c>
       <c r="G3">
-        <v>20.70409893288122</v>
+        <v>16.45058342475317</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>39.90736226231107</v>
+      </c>
+      <c r="C4">
         <v>20.18527547537786</v>
-      </c>
-      <c r="C4">
-        <v>39.90736226231107</v>
       </c>
       <c r="D4">
         <v>4.954106280193237</v>
       </c>
       <c r="E4">
-        <v>12.60849703060758</v>
+        <v>24.92766864626161</v>
       </c>
       <c r="F4">
         <v>62.4638343231308</v>
       </c>
       <c r="G4">
-        <v>24.92766864626161</v>
+        <v>12.60849703060758</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>31.49492017416546</v>
+      </c>
+      <c r="C5">
         <v>27.78832198280674</v>
-      </c>
-      <c r="C5">
-        <v>31.49492017416546</v>
       </c>
       <c r="D5">
         <v>3.598633989554038</v>
       </c>
       <c r="E5">
-        <v>17.44585406883017</v>
+        <v>19.77290250227799</v>
       </c>
       <c r="F5">
         <v>62.78124342889185</v>
       </c>
       <c r="G5">
-        <v>19.77290250227799</v>
+        <v>17.44585406883017</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>32.19486081370449</v>
+      </c>
+      <c r="C6">
         <v>20.10706638115632</v>
-      </c>
-      <c r="C6">
-        <v>32.19486081370449</v>
       </c>
       <c r="D6">
         <v>4.973375931842385</v>
       </c>
       <c r="E6">
-        <v>13.20210896309314</v>
+        <v>21.13884007029877</v>
       </c>
       <c r="F6">
         <v>65.65905096660809</v>
       </c>
       <c r="G6">
-        <v>21.13884007029877</v>
+        <v>13.20210896309314</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>32.43471647088651</v>
+      </c>
+      <c r="C7">
         <v>28.65432829093778</v>
-      </c>
-      <c r="C7">
-        <v>32.43471647088651</v>
       </c>
       <c r="D7">
         <v>3.489874164372788</v>
       </c>
       <c r="E7">
-        <v>17.78788143743989</v>
+        <v>20.13465069511236</v>
       </c>
       <c r="F7">
         <v>62.07746786744775</v>
       </c>
       <c r="G7">
-        <v>20.13465069511236</v>
+        <v>17.78788143743989</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>36.52365236523652</v>
+      </c>
+      <c r="C8">
         <v>41.29079574624129</v>
-      </c>
-      <c r="C8">
-        <v>36.52365236523652</v>
       </c>
       <c r="D8">
         <v>2.421847246891652</v>
       </c>
       <c r="E8">
-        <v>23.22128273870901</v>
+        <v>20.54031759125593</v>
       </c>
       <c r="F8">
         <v>56.23839967003506</v>
       </c>
       <c r="G8">
-        <v>20.54031759125593</v>
+        <v>23.22128273870901</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>34.21227564812763</v>
+      </c>
+      <c r="C9">
         <v>29.71415909594505</v>
-      </c>
-      <c r="C9">
-        <v>34.21227564812763</v>
       </c>
       <c r="D9">
         <v>3.365398956002983</v>
       </c>
       <c r="E9">
-        <v>18.12652068126521</v>
+        <v>20.87050554203839</v>
       </c>
       <c r="F9">
         <v>61.00297377669641</v>
       </c>
       <c r="G9">
-        <v>20.87050554203839</v>
+        <v>18.12652068126521</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>32.1754774425685</v>
+      </c>
+      <c r="C10">
         <v>31.23443122059231</v>
-      </c>
-      <c r="C10">
-        <v>32.1754774425685</v>
       </c>
       <c r="D10">
         <v>3.201595037660611</v>
       </c>
       <c r="E10">
-        <v>19.11415989159891</v>
+        <v>19.6900406504065</v>
       </c>
       <c r="F10">
         <v>61.19579945799457</v>
       </c>
       <c r="G10">
-        <v>19.6900406504065</v>
+        <v>19.11415989159891</v>
       </c>
     </row>
   </sheetData>
